--- a/Permisos_por_Area_WebInternaSP.xlsx
+++ b/Permisos_por_Area_WebInternaSP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Wolcan\Claude\Projects\web_interna_sp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D8AF72-FF33-47E0-8465-DC682B98D344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAEA63F-DFF9-4479-B0FF-FC206724DDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="195">
   <si>
     <t>Permisos por área — Web Interna SP</t>
   </si>
@@ -122,6 +122,15 @@
   </si>
   <si>
     <t>Organigrama institucional: responsables por área y funciones.</t>
+  </si>
+  <si>
+    <t>informes-mkt</t>
+  </si>
+  <si>
+    <t>Informes e indicadores de MKT</t>
+  </si>
+  <si>
+    <t>Informe mensual de clientes que concretaron una venta: leads nuevos, cartera y canal de adquisición.</t>
   </si>
   <si>
     <t>pizarra</t>
@@ -515,6 +524,11 @@
   <si>
     <t>Directorio
 de Áreas</t>
+  </si>
+  <si>
+    <t>Informes e
+indicadores
+de MKT</t>
   </si>
   <si>
     <t>Pizarra
@@ -746,7 +760,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -787,6 +801,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1192,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1278,70 +1297,80 @@
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="8"/>
+      <c r="F5" s="20"/>
     </row>
     <row r="6" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="E6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
+    </row>
+    <row r="8" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
@@ -1382,6 +1411,14 @@
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1407,748 +1444,748 @@
         <v>16</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="E3" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="E4" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C5" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="E6" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F6" s="10"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="E7" s="10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F8" s="10"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="D9" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>75</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F15" s="10"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="E17" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>90</v>
-      </c>
       <c r="D18" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F18" s="10"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>93</v>
-      </c>
       <c r="D19" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F20" s="10"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F21" s="10"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B22" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>100</v>
-      </c>
       <c r="D22" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C24" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="E24" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B25" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>108</v>
       </c>
       <c r="F25" s="10"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F26" s="10"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F27" s="10"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>115</v>
-      </c>
       <c r="D28" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C29" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="E29" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="D30" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F30" s="10"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F31" s="10"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>126</v>
-      </c>
       <c r="D32" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F34" s="10"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C35" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="E35" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>136</v>
-      </c>
       <c r="D36" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F36" s="10"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>139</v>
-      </c>
       <c r="D37" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F38" s="10"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F39" s="10"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B40" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>147</v>
-      </c>
       <c r="D40" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C42" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D42" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="E42" s="10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
@@ -2160,7 +2197,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2168,754 +2205,815 @@
     <col min="3" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>166</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="G2" s="13"/>
+        <v>171</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>171</v>
+      </c>
       <c r="H2" s="13"/>
-      <c r="I2" s="17" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I2" s="13"/>
+      <c r="J2" s="17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="G3" s="13"/>
+        <v>173</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="H3" s="13"/>
-      <c r="I3" s="17" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I3" s="13"/>
+      <c r="J3" s="17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
-      <c r="I4" s="18"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I4" s="13"/>
+      <c r="J4" s="18"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="F5" s="22"/>
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
-      <c r="I5" s="18"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I5" s="13"/>
+      <c r="J5" s="18"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
+      <c r="F6" s="22"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
-      <c r="I6" s="18"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I6" s="13"/>
+      <c r="J6" s="18"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="F7" s="22"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
-      <c r="I7" s="18"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I7" s="13"/>
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="G8" s="13"/>
+        <v>173</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="H8" s="13"/>
-      <c r="I8" s="17" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I8" s="13"/>
+      <c r="J8" s="17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
+      <c r="F9" s="22"/>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
-      <c r="I9" s="18"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I9" s="13"/>
+      <c r="J9" s="18"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="F10" s="22"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
-      <c r="I10" s="18"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I10" s="13"/>
+      <c r="J10" s="18"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="F11" s="22"/>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
-      <c r="I11" s="18"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I11" s="13"/>
+      <c r="J11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="F12" s="22"/>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
-      <c r="I12" s="18"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I12" s="13"/>
+      <c r="J12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="F13" s="22"/>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
-      <c r="I13" s="18"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I13" s="13"/>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
+      <c r="F14" s="22"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
-      <c r="I14" s="18"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I14" s="13"/>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="F15" s="22"/>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
-      <c r="I15" s="18"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I15" s="13"/>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="G16" s="13"/>
+        <v>171</v>
+      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="H16" s="13"/>
-      <c r="I16" s="17" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I16" s="13"/>
+      <c r="J16" s="17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
+      <c r="F17" s="12" t="s">
+        <v>171</v>
+      </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
-      <c r="I17" s="18"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I17" s="13"/>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
+      <c r="F18" s="22"/>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
-      <c r="I18" s="18"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I18" s="13"/>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
+      <c r="F19" s="22"/>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
-      <c r="I19" s="18"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I19" s="13"/>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" s="13"/>
+        <v>102</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>171</v>
+      </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
+      <c r="F20" s="12" t="s">
+        <v>171</v>
+      </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
-      <c r="I20" s="18"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I20" s="13"/>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
+      <c r="F21" s="22"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
-      <c r="I21" s="18"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I21" s="13"/>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+      <c r="F22" s="22"/>
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
-      <c r="I22" s="18"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I22" s="13"/>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
+      <c r="F23" s="22"/>
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
-      <c r="I23" s="18"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I23" s="13"/>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
+      <c r="F24" s="22"/>
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
-      <c r="I24" s="18"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I24" s="13"/>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
+      <c r="F25" s="22"/>
       <c r="G25" s="13"/>
       <c r="H25" s="13"/>
-      <c r="I25" s="18"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I25" s="13"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
+      <c r="F26" s="22"/>
       <c r="G26" s="13"/>
       <c r="H26" s="13"/>
-      <c r="I26" s="18"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I26" s="13"/>
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
+      <c r="F27" s="22"/>
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
-      <c r="I27" s="18"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I27" s="13"/>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
+      <c r="F28" s="22"/>
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
-      <c r="I28" s="18"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I28" s="13"/>
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="G29" s="13"/>
+        <v>173</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="H29" s="13"/>
-      <c r="I29" s="17" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I29" s="13"/>
+      <c r="J29" s="17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
+      <c r="F30" s="22"/>
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
-      <c r="I30" s="18"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I30" s="13"/>
+      <c r="J30" s="18"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
+      <c r="F31" s="22"/>
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
-      <c r="I31" s="18"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I31" s="13"/>
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
+      <c r="F32" s="22"/>
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
-      <c r="I32" s="18"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I32" s="13"/>
+      <c r="J32" s="18"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
+      <c r="F33" s="22"/>
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
-      <c r="I33" s="18"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I33" s="13"/>
+      <c r="J33" s="18"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
+      <c r="F34" s="22"/>
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
-      <c r="I34" s="18"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I34" s="13"/>
+      <c r="J34" s="18"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
       <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
+      <c r="F35" s="22"/>
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
-      <c r="I35" s="18"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I35" s="13"/>
+      <c r="J35" s="18"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
+      <c r="F36" s="22"/>
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
-      <c r="I36" s="18"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I36" s="13"/>
+      <c r="J36" s="18"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
+      <c r="F37" s="22"/>
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
-      <c r="I37" s="18"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I37" s="13"/>
+      <c r="J37" s="18"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
+      <c r="F38" s="22"/>
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
-      <c r="I38" s="18"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I38" s="13"/>
+      <c r="J38" s="18"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
+      <c r="F39" s="22"/>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
-      <c r="I39" s="18"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I39" s="13"/>
+      <c r="J39" s="18"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
+      <c r="F40" s="22"/>
       <c r="G40" s="13"/>
       <c r="H40" s="13"/>
-      <c r="I40" s="18"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I40" s="13"/>
+      <c r="J40" s="18"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
       <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
+      <c r="F41" s="22"/>
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
-      <c r="I41" s="18"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I41" s="13"/>
+      <c r="J41" s="18"/>
+    </row>
+    <row r="42" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="I42" s="17" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
       <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
+      <c r="F43" s="22"/>
       <c r="G43" s="13"/>
       <c r="H43" s="13"/>
-      <c r="I43" s="18"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I44" s="18"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I43" s="13"/>
+      <c r="J43" s="18"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J44" s="18"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="I45" s="18"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+      <c r="J45" s="18"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="I46" s="18"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+      <c r="J46" s="18"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="19" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C2:H43" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:I43" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Ver,Editar"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Permisos_por_Area_WebInternaSP.xlsx
+++ b/Permisos_por_Area_WebInternaSP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Wolcan\Claude\Projects\web_interna_sp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAEA63F-DFF9-4479-B0FF-FC206724DDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2ABBEB-FA62-4E86-95F1-903B86E69F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="199">
   <si>
     <t>Permisos por área — Web Interna SP</t>
   </si>
@@ -131,6 +131,15 @@
   </si>
   <si>
     <t>Informe mensual de clientes que concretaron una venta: leads nuevos, cartera y canal de adquisición.</t>
+  </si>
+  <si>
+    <t>comunicacion-receptoras</t>
+  </si>
+  <si>
+    <t>Comunicación Receptoras</t>
+  </si>
+  <si>
+    <t>Análisis de comunicación telefónica de clientes vía receptoras Bosch D6600: clientes identificados por señales de eventos.</t>
   </si>
   <si>
     <t>pizarra</t>
@@ -529,6 +538,10 @@
     <t>Informes e
 indicadores
 de MKT</t>
+  </si>
+  <si>
+    <t>Comunicación
+Receptoras</t>
   </si>
   <si>
     <t>Pizarra
@@ -760,7 +773,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -806,6 +819,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1211,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1315,70 +1334,80 @@
       <c r="F5" s="20"/>
     </row>
     <row r="6" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="8"/>
+      <c r="F6" s="20"/>
     </row>
     <row r="7" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="B8" s="8" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
+    </row>
+    <row r="9" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
@@ -1419,6 +1448,14 @@
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1444,748 +1481,748 @@
         <v>16</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="E3" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="E4" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C5" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C6" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="E6" s="10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F6" s="10"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="E7" s="10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F8" s="10"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>73</v>
-      </c>
       <c r="D9" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>81</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F15" s="10"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="E17" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>93</v>
-      </c>
       <c r="D18" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F18" s="10"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>96</v>
-      </c>
       <c r="D19" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F20" s="10"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F21" s="10"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B22" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>103</v>
-      </c>
       <c r="D22" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C24" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="E24" s="10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B25" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>111</v>
       </c>
       <c r="F25" s="10"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F26" s="10"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F27" s="10"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>118</v>
-      </c>
       <c r="D28" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C29" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="E29" s="10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>123</v>
-      </c>
       <c r="D30" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F30" s="10"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F31" s="10"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>129</v>
-      </c>
       <c r="D32" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F34" s="10"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C35" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D35" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="E35" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>139</v>
-      </c>
       <c r="D36" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F36" s="10"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>142</v>
-      </c>
       <c r="D37" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F38" s="10"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F39" s="10"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B40" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>150</v>
-      </c>
       <c r="D40" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C42" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="E42" s="10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
@@ -2197,7 +2234,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2205,815 +2242,858 @@
     <col min="3" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>170</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="H2" s="13"/>
+        <v>175</v>
+      </c>
+      <c r="G2" s="23"/>
+      <c r="H2" s="12" t="s">
+        <v>175</v>
+      </c>
       <c r="I2" s="13"/>
-      <c r="J2" s="17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="J2" s="13"/>
+      <c r="K2" s="17" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H3" s="13"/>
+        <v>177</v>
+      </c>
+      <c r="G3" s="23"/>
+      <c r="H3" s="12" t="s">
+        <v>177</v>
+      </c>
       <c r="I3" s="13"/>
-      <c r="J3" s="17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J3" s="13"/>
+      <c r="K3" s="17" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="22"/>
-      <c r="G4" s="13"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
-      <c r="J4" s="18"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J4" s="13"/>
+      <c r="K4" s="18"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="22"/>
-      <c r="G5" s="13"/>
+      <c r="G5" s="23"/>
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
-      <c r="J5" s="18"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J5" s="13"/>
+      <c r="K5" s="18"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="22"/>
-      <c r="G6" s="13"/>
+      <c r="G6" s="23"/>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
-      <c r="J6" s="18"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J6" s="13"/>
+      <c r="K6" s="18"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
       <c r="F7" s="22"/>
-      <c r="G7" s="13"/>
+      <c r="G7" s="23"/>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
-      <c r="J7" s="18"/>
-    </row>
-    <row r="8" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="J7" s="13"/>
+      <c r="K7" s="18"/>
+    </row>
+    <row r="8" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" s="13"/>
+        <v>177</v>
+      </c>
+      <c r="G8" s="23"/>
+      <c r="H8" s="12" t="s">
+        <v>177</v>
+      </c>
       <c r="I8" s="13"/>
-      <c r="J8" s="17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J8" s="13"/>
+      <c r="K8" s="17" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="22"/>
-      <c r="G9" s="13"/>
+      <c r="G9" s="23"/>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
-      <c r="J9" s="18"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J9" s="13"/>
+      <c r="K9" s="18"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="22"/>
-      <c r="G10" s="13"/>
+      <c r="G10" s="23"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
-      <c r="J10" s="18"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J10" s="13"/>
+      <c r="K10" s="18"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="22"/>
-      <c r="G11" s="13"/>
+      <c r="G11" s="23"/>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
-      <c r="J11" s="18"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J11" s="13"/>
+      <c r="K11" s="18"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="13"/>
+      <c r="G12" s="23"/>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
-      <c r="J12" s="18"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J12" s="13"/>
+      <c r="K12" s="18"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="22"/>
-      <c r="G13" s="13"/>
+      <c r="G13" s="23"/>
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
-      <c r="J13" s="18"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J13" s="13"/>
+      <c r="K13" s="18"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="22"/>
-      <c r="G14" s="13"/>
+      <c r="G14" s="23"/>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
-      <c r="J14" s="18"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J14" s="13"/>
+      <c r="K14" s="18"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="13"/>
+      <c r="G15" s="23"/>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
-      <c r="J15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="J15" s="13"/>
+      <c r="K15" s="18"/>
+    </row>
+    <row r="16" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F16" s="21"/>
-      <c r="G16" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H16" s="13"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="12" t="s">
+        <v>177</v>
+      </c>
       <c r="I16" s="13"/>
-      <c r="J16" s="17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J16" s="13"/>
+      <c r="K16" s="17" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
       <c r="F17" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="G17" s="13"/>
+        <v>175</v>
+      </c>
+      <c r="G17" s="23"/>
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="18"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J17" s="13"/>
+      <c r="K17" s="18"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="22"/>
-      <c r="G18" s="13"/>
+      <c r="G18" s="23"/>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
-      <c r="J18" s="18"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J18" s="13"/>
+      <c r="K18" s="18"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
       <c r="F19" s="22"/>
-      <c r="G19" s="13"/>
+      <c r="G19" s="23"/>
       <c r="H19" s="13"/>
       <c r="I19" s="13"/>
-      <c r="J19" s="18"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J19" s="13"/>
+      <c r="K19" s="18"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="G20" s="13"/>
+        <v>175</v>
+      </c>
+      <c r="G20" s="23"/>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
-      <c r="J20" s="18"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J20" s="13"/>
+      <c r="K20" s="18"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
       <c r="F21" s="22"/>
-      <c r="G21" s="13"/>
+      <c r="G21" s="23"/>
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
-      <c r="J21" s="18"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J21" s="13"/>
+      <c r="K21" s="18"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="22"/>
-      <c r="G22" s="13"/>
+      <c r="G22" s="23"/>
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J22" s="13"/>
+      <c r="K22" s="18"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="22"/>
-      <c r="G23" s="13"/>
+      <c r="G23" s="23"/>
       <c r="H23" s="13"/>
       <c r="I23" s="13"/>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J23" s="13"/>
+      <c r="K23" s="18"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
       <c r="F24" s="22"/>
-      <c r="G24" s="13"/>
+      <c r="G24" s="23"/>
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J24" s="13"/>
+      <c r="K24" s="18"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="22"/>
-      <c r="G25" s="13"/>
+      <c r="G25" s="23"/>
       <c r="H25" s="13"/>
       <c r="I25" s="13"/>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J25" s="13"/>
+      <c r="K25" s="18"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
       <c r="F26" s="22"/>
-      <c r="G26" s="13"/>
+      <c r="G26" s="23"/>
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J26" s="13"/>
+      <c r="K26" s="18"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
       <c r="F27" s="22"/>
-      <c r="G27" s="13"/>
+      <c r="G27" s="23"/>
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J27" s="13"/>
+      <c r="K27" s="18"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
       <c r="F28" s="22"/>
-      <c r="G28" s="13"/>
+      <c r="G28" s="23"/>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="29" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="J28" s="13"/>
+      <c r="K28" s="18"/>
+    </row>
+    <row r="29" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>173</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
       <c r="G29" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H29" s="13"/>
+        <v>175</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>175</v>
+      </c>
       <c r="I29" s="13"/>
-      <c r="J29" s="17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J29" s="13"/>
+      <c r="K29" s="17" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
       <c r="F30" s="22"/>
-      <c r="G30" s="13"/>
+      <c r="G30" s="23"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
-      <c r="J30" s="18"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J30" s="13"/>
+      <c r="K30" s="18"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
       <c r="F31" s="22"/>
-      <c r="G31" s="13"/>
+      <c r="G31" s="23"/>
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
-      <c r="J31" s="18"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J31" s="13"/>
+      <c r="K31" s="18"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
       <c r="F32" s="22"/>
-      <c r="G32" s="13"/>
+      <c r="G32" s="23"/>
       <c r="H32" s="13"/>
       <c r="I32" s="13"/>
-      <c r="J32" s="18"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J32" s="13"/>
+      <c r="K32" s="18"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
       <c r="F33" s="22"/>
-      <c r="G33" s="13"/>
+      <c r="G33" s="23"/>
       <c r="H33" s="13"/>
       <c r="I33" s="13"/>
-      <c r="J33" s="18"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J33" s="13"/>
+      <c r="K33" s="18"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
       <c r="F34" s="22"/>
-      <c r="G34" s="13"/>
+      <c r="G34" s="23"/>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
-      <c r="J34" s="18"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J34" s="13"/>
+      <c r="K34" s="18"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
       <c r="E35" s="13"/>
       <c r="F35" s="22"/>
-      <c r="G35" s="13"/>
+      <c r="G35" s="23"/>
       <c r="H35" s="13"/>
       <c r="I35" s="13"/>
-      <c r="J35" s="18"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J35" s="13"/>
+      <c r="K35" s="18"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
       <c r="F36" s="22"/>
-      <c r="G36" s="13"/>
+      <c r="G36" s="23"/>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
-      <c r="J36" s="18"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J36" s="13"/>
+      <c r="K36" s="18"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
       <c r="F37" s="22"/>
-      <c r="G37" s="13"/>
+      <c r="G37" s="23"/>
       <c r="H37" s="13"/>
       <c r="I37" s="13"/>
-      <c r="J37" s="18"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J37" s="13"/>
+      <c r="K37" s="18"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
       <c r="F38" s="22"/>
-      <c r="G38" s="13"/>
+      <c r="G38" s="23"/>
       <c r="H38" s="13"/>
       <c r="I38" s="13"/>
-      <c r="J38" s="18"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J38" s="13"/>
+      <c r="K38" s="18"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
       <c r="F39" s="22"/>
-      <c r="G39" s="13"/>
+      <c r="G39" s="23"/>
       <c r="H39" s="13"/>
       <c r="I39" s="13"/>
-      <c r="J39" s="18"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J39" s="13"/>
+      <c r="K39" s="18"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="22"/>
-      <c r="G40" s="13"/>
+      <c r="G40" s="23"/>
       <c r="H40" s="13"/>
       <c r="I40" s="13"/>
-      <c r="J40" s="18"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J40" s="13"/>
+      <c r="K40" s="18"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
       <c r="E41" s="13"/>
       <c r="F41" s="22"/>
-      <c r="G41" s="13"/>
+      <c r="G41" s="23"/>
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
-      <c r="J41" s="18"/>
-    </row>
-    <row r="42" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="J41" s="13"/>
+      <c r="K41" s="18"/>
+    </row>
+    <row r="42" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>173</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="G42" s="24"/>
       <c r="H42" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="J42" s="17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
       <c r="E43" s="13"/>
       <c r="F43" s="22"/>
-      <c r="G43" s="13"/>
+      <c r="G43" s="23"/>
       <c r="H43" s="13"/>
       <c r="I43" s="13"/>
-      <c r="J43" s="18"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J44" s="18"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J43" s="13"/>
+      <c r="K43" s="18"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K44" s="18"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="J45" s="18"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+      <c r="K45" s="18"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="J46" s="18"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+      <c r="K46" s="18"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="19" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C2:I43" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:J43" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Ver,Editar"</formula1>
     </dataValidation>
   </dataValidations>
